--- a/PRP申請書類 自動転記ツール/01_input【ヒアリングシートをここへ】/略歴書_大井知泉先生.xlsx
+++ b/PRP申請書類 自動転記ツール/01_input【ヒアリングシートをここへ】/略歴書_大井知泉先生.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="略歴書（PRP）" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,17 +29,11 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
-    <t>山中 次郎</t>
-  </si>
-  <si>
     <t>氏名</t>
   </si>
   <si>
     <t>医師略歴書
 （再生医療等を行う医師）</t>
-  </si>
-  <si>
-    <t>やまなか　じろう</t>
   </si>
   <si>
     <t>生年月日</t>
@@ -145,6 +139,14 @@
   <si>
     <t>医籍番号：第・・・・・号　　
 免許取得日：・・・年・・月・・日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おおい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大井　知泉</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -300,11 +302,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -577,7 +579,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -593,147 +595,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="55.35" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="11"/>
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="12"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4"/>
       <c r="B3" s="2" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="36">
       <c r="A7" s="4"/>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="237.45" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="93.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="56.25" customHeight="1">
       <c r="A13" s="9"/>
       <c r="B13" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9"/>
       <c r="B14" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="150" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="36" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="93.75" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="9"/>
       <c r="B18" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="56.25" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="9"/>
       <c r="B20" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="75" customHeight="1">
-      <c r="A21" s="12"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
